--- a/templates/日报模板.xlsx
+++ b/templates/日报模板.xlsx
@@ -27,15 +27,22 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -58,7 +65,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">

--- a/templates/日报模板.xlsx
+++ b/templates/日报模板.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\idea-workspase-skills\daily-merge\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B9AFB31-CB7D-4B18-98FD-D00A8F2555BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D21BFCB-5161-4342-8F09-E6F8A924EFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1656" yWindow="0" windowWidth="34128" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="张三" sheetId="1" r:id="rId1"/>
+    <sheet name="胡志伟" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -316,7 +316,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -368,17 +368,11 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -704,10 +698,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" s="8" customFormat="1" ht="15.6">
-      <c r="A2" s="17"/>
-      <c r="B2" s="18"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="7"/>
-      <c r="D2" s="19"/>
+      <c r="D2" s="18"/>
       <c r="E2" s="9"/>
       <c r="F2" s="10"/>
       <c r="G2" s="10"/>
@@ -717,10 +711,9 @@
       <c r="L2" s="7"/>
     </row>
     <row r="3" spans="1:14" s="8" customFormat="1" ht="15.6">
-      <c r="A3" s="17"/>
-      <c r="B3" s="20"/>
+      <c r="A3" s="10"/>
       <c r="C3" s="7"/>
-      <c r="D3" s="19"/>
+      <c r="D3" s="18"/>
       <c r="E3" s="9"/>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
@@ -729,24 +722,23 @@
       <c r="K3" s="6"/>
       <c r="L3" s="7"/>
     </row>
-    <row r="4" spans="1:14" s="21" customFormat="1" ht="15.6">
-      <c r="A4" s="17"/>
-      <c r="B4" s="20"/>
+    <row r="4" spans="1:14" s="19" customFormat="1" ht="15.6">
+      <c r="A4" s="10"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="7"/>
-      <c r="D4" s="19"/>
+      <c r="D4" s="18"/>
       <c r="E4" s="9"/>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
       <c r="H4" s="6"/>
       <c r="J4" s="10"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="22"/>
+      <c r="L4" s="20"/>
     </row>
     <row r="5" spans="1:14" s="8" customFormat="1" ht="15.6">
-      <c r="A5" s="17"/>
-      <c r="B5" s="20"/>
+      <c r="A5" s="10"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="19"/>
+      <c r="D5" s="18"/>
       <c r="E5" s="9"/>
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
@@ -756,10 +748,9 @@
       <c r="L5" s="7"/>
     </row>
     <row r="6" spans="1:14" s="8" customFormat="1" ht="15.6">
-      <c r="A6" s="17"/>
-      <c r="B6" s="20"/>
+      <c r="A6" s="10"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="19"/>
+      <c r="D6" s="18"/>
       <c r="E6" s="9"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
@@ -769,10 +760,9 @@
       <c r="L6" s="7"/>
     </row>
     <row r="7" spans="1:14" s="8" customFormat="1" ht="15.6">
-      <c r="A7" s="17"/>
-      <c r="B7" s="20"/>
+      <c r="A7" s="10"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="19"/>
+      <c r="D7" s="18"/>
       <c r="E7" s="9"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
@@ -783,10 +773,9 @@
       <c r="L7" s="7"/>
     </row>
     <row r="8" spans="1:14" s="8" customFormat="1" ht="15.6">
-      <c r="A8" s="17"/>
-      <c r="B8" s="20"/>
+      <c r="A8" s="10"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="19"/>
+      <c r="D8" s="18"/>
       <c r="E8" s="9"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
@@ -797,10 +786,9 @@
       <c r="L8" s="7"/>
     </row>
     <row r="9" spans="1:14" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A9" s="17"/>
-      <c r="B9" s="20"/>
+      <c r="A9" s="10"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="19"/>
+      <c r="D9" s="18"/>
       <c r="E9" s="9"/>
       <c r="F9" s="10"/>
       <c r="G9" s="11"/>

--- a/templates/日报模板.xlsx
+++ b/templates/日报模板.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\idea-workspase-skills\daily-merge\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D21BFCB-5161-4342-8F09-E6F8A924EFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7C993D-9B46-4B7C-BA87-72F49F4C1CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1656" yWindow="0" windowWidth="34128" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="胡志伟" sheetId="1" r:id="rId1"/>
+    <sheet name="胡志伟" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>实际完成时间</t>
   </si>
@@ -176,10 +176,6 @@
   </si>
   <si>
     <t>2、前一天已完成的任务不需要重新出现在当天的记录中（若之前的任务完成后有bug需要修改，需要新建一条记录，复制之前任务的描述后面增加【bug】字样，并在插队序号中填写之前的任务序号，主序号依然递增）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>8、开会和沟通也当作任务记录时常</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -634,26 +630,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="张三"/>
-  <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="18" customHeight="1"/>
-  <cols>
-    <col min="2" max="2" width="22.54296875" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="59.26953125" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.36328125" customWidth="1"/>
-    <col min="7" max="7" width="15.90625" customWidth="1"/>
-    <col min="8" max="8" width="13.90625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="24.26953125" customWidth="1"/>
-    <col min="11" max="11" width="14.81640625" style="5" customWidth="1"/>
-    <col min="12" max="12" width="12" style="1" customWidth="1"/>
-    <col min="13" max="13" width="41.81640625" customWidth="1"/>
-    <col min="14" max="14" width="53.7265625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A49D6851-1A1C-4785-819D-8FAD6FAF2B3F}">
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="57" customHeight="1">
+    <row r="1" spans="1:14" ht="78">
       <c r="A1" s="12" t="s">
         <v>5</v>
       </c>
@@ -676,7 +657,7 @@
         <v>11</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>3</v>
@@ -697,7 +678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="8" customFormat="1" ht="15.6">
+    <row r="2" spans="1:14">
       <c r="A2" s="10"/>
       <c r="B2" s="17"/>
       <c r="C2" s="7"/>
@@ -706,23 +687,30 @@
       <c r="F2" s="10"/>
       <c r="G2" s="10"/>
       <c r="H2" s="6"/>
+      <c r="I2" s="8"/>
       <c r="J2" s="10"/>
       <c r="K2" s="6"/>
       <c r="L2" s="7"/>
-    </row>
-    <row r="3" spans="1:14" s="8" customFormat="1" ht="15.6">
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="10"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="7"/>
       <c r="D3" s="18"/>
       <c r="E3" s="9"/>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
       <c r="H3" s="6"/>
+      <c r="I3" s="8"/>
       <c r="J3" s="10"/>
       <c r="K3" s="6"/>
       <c r="L3" s="7"/>
-    </row>
-    <row r="4" spans="1:14" s="19" customFormat="1" ht="15.6">
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="10"/>
       <c r="B4" s="8"/>
       <c r="C4" s="7"/>
@@ -731,36 +719,48 @@
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
       <c r="H4" s="6"/>
+      <c r="I4" s="19"/>
       <c r="J4" s="10"/>
       <c r="K4" s="6"/>
       <c r="L4" s="20"/>
-    </row>
-    <row r="5" spans="1:14" s="8" customFormat="1" ht="15.6">
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="10"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="7"/>
       <c r="D5" s="18"/>
       <c r="E5" s="9"/>
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
       <c r="H5" s="6"/>
+      <c r="I5" s="8"/>
       <c r="J5" s="10"/>
       <c r="K5" s="6"/>
       <c r="L5" s="7"/>
-    </row>
-    <row r="6" spans="1:14" s="8" customFormat="1" ht="15.6">
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="10"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="7"/>
       <c r="D6" s="18"/>
       <c r="E6" s="9"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="6"/>
+      <c r="I6" s="8"/>
       <c r="J6" s="10"/>
       <c r="K6" s="6"/>
       <c r="L6" s="7"/>
-    </row>
-    <row r="7" spans="1:14" s="8" customFormat="1" ht="15.6">
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="10"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="7"/>
       <c r="D7" s="18"/>
       <c r="E7" s="9"/>
@@ -771,9 +771,12 @@
       <c r="J7" s="11"/>
       <c r="K7" s="6"/>
       <c r="L7" s="7"/>
-    </row>
-    <row r="8" spans="1:14" s="8" customFormat="1" ht="15.6">
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="10"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="7"/>
       <c r="D8" s="18"/>
       <c r="E8" s="9"/>
@@ -784,9 +787,12 @@
       <c r="J8" s="11"/>
       <c r="K8" s="6"/>
       <c r="L8" s="7"/>
-    </row>
-    <row r="9" spans="1:14" s="8" customFormat="1" ht="18" customHeight="1">
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="10"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="7"/>
       <c r="D9" s="18"/>
       <c r="E9" s="9"/>
@@ -797,63 +803,115 @@
       <c r="J9" s="11"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" ht="18" customHeight="1">
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
-    </row>
-    <row r="11" spans="1:14" ht="18" customHeight="1">
+      <c r="C10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="H10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
-    </row>
-    <row r="12" spans="1:14" ht="18" customHeight="1">
+      <c r="C11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="H11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
-    </row>
-    <row r="13" spans="1:14" ht="29.25" customHeight="1">
+      <c r="C12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="H12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" ht="62.4">
       <c r="A13" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="18" customHeight="1">
+      <c r="C13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="H13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" spans="1:14">
       <c r="B14" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="18" customHeight="1">
+      <c r="C14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="H14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" spans="1:14">
       <c r="B15" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="18" customHeight="1">
+      <c r="C15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="H15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" spans="1:14">
       <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="2:2" ht="18" customHeight="1">
+      <c r="C16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="H16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" spans="2:12">
       <c r="B17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="2:2" ht="18" customHeight="1">
+      <c r="C17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="H17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="1"/>
+    </row>
+    <row r="18" spans="2:12">
       <c r="B18" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="2:2" ht="18" customHeight="1">
+      <c r="C18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="H18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="1"/>
+    </row>
+    <row r="19" spans="2:12">
       <c r="B19" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="2:2" ht="18" customHeight="1">
+      <c r="C19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="H19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" spans="2:12">
       <c r="B20" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="2:2" ht="18" customHeight="1">
-      <c r="B21" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="C20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="H20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
